--- a/业务合作费.xlsx
+++ b/业务合作费.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18460"/>
+    <workbookView windowWidth="28800" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="业务合作费" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
-  <si>
-    <t>业务合作服务费</t>
-  </si>
-  <si>
-    <t>与订单清算挂钩，清算后立即计算成本</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+  <si>
+    <t>费用名称</t>
+  </si>
+  <si>
+    <t>条件说明</t>
+  </si>
+  <si>
+    <t>厂家/集团</t>
+  </si>
+  <si>
+    <t>收费规则</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>业务合作服务费
+与订单清算挂钩，清算后立即计算成本；
+新规：仲裁退车系统收取业务合作服务费，同车(同vin码）下次成交不再收取业务合作服务费</t>
+  </si>
+  <si>
+    <t>订单清分后统计
+集团=理想汽车</t>
   </si>
   <si>
     <t>集团：理想汽车</t>
@@ -307,16 +325,34 @@
     <t>系统计算</t>
   </si>
   <si>
+    <t>已有</t>
+  </si>
+  <si>
+    <t>订单清分后统计
+集团=深圳大茂鹏鸿</t>
+  </si>
+  <si>
     <t>集团：深圳大茂鹏鸿</t>
   </si>
   <si>
     <t>300元/台</t>
   </si>
   <si>
+    <t>订单清分后统计
+集团=利泰集团</t>
+  </si>
+  <si>
     <t>集团：利泰集团</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>每月1号统计上月的返佣情况
 情况1：成交台数</t>
     </r>
@@ -367,56 +403,252 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>门店ID：3872</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>订单清分后统计
+门店=3872，广东唯普汽车科技股份有限公司-鸿蒙智行</t>
+  </si>
+  <si>
+    <t>门店ID：3872
+全称：广东唯普汽车科技股份有限公司-鸿蒙智行</t>
+  </si>
+  <si>
+    <t>200元/台</t>
+  </si>
+  <si>
+    <t>订单清分后统计</t>
+  </si>
+  <si>
+    <t>所属小区：四川-成都、重庆-其他、四川-重启</t>
+  </si>
+  <si>
+    <t>唯普毛利*65%</t>
+  </si>
+  <si>
+    <t>订单清分后统计
+1、门店id=4296，门店全称：浙江零跑汽车销售服务有限公司-广州</t>
+  </si>
+  <si>
+    <t>浙江零跑汽车销售服务有限公司-广州</t>
+  </si>
+  <si>
+    <t>合同价≤5k, 0元/台
+5K＜合同价≤10W, 700元/台
+10W＜合同价, 1000元/台</t>
+  </si>
+  <si>
+    <t>新增</t>
+  </si>
+  <si>
+    <t>订单清分后统计：
+1、通过聚合拍平台推送车辆
+2、门店总店=“长城”或“长城V2”
+3、车辆已关联厂家</t>
+  </si>
+  <si>
+    <t>门店总店：长城 或 长城V2</t>
+  </si>
+  <si>
+    <t>聚合拍平台推送到车唯拍成交的车辆：
+成交车价＜1W, 50元/台
+1W≤成交车价＜3W, 100元/台
+3W≤成交车价＜5W, 150元/台
+5W≤成交车价＜10W, 200元/台
+10W≤成交车价, 300元/台</t>
+  </si>
+  <si>
+    <t>订单清分后统计：
+1、通过聚合拍平台推送车辆
+2、门店总店=“一汽红旗”或“一汽大众”
+3、车辆已关联厂家
+4、区分报废车和非报废车</t>
+  </si>
+  <si>
+    <t xml:space="preserve">门店总店：一汽红旗、一汽大众
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>全称：广东唯普汽车科技股份有限公司-鸿蒙智行</t>
-    </r>
-  </si>
-  <si>
-    <t>200元/台</t>
-  </si>
-  <si>
-    <r>
-      <t>原规则：仲裁退车：系统会自动生成对冲的负数成本，用来规避同一台车计算多次服务费的情况；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-新规则：仲裁退车：系统收取业务合作服务费，同车(同vin码）下次不再收取业务合作服务费</t>
-    </r>
+  </si>
+  <si>
+    <t>聚合拍平台推送的成交车辆：
+非拆解车辆（非报废）：200元/辆
+拆解车辆（报废）：100元/辆</t>
+  </si>
+  <si>
+    <r>
+      <t>订单清分后统计成交车辆：
+1、集团=长久集团
+2、成交台数(不抛仲裁退车)：按照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>合同年计算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>；比如26年的成交台数中的合同年指统计：2025.7.31-至今的成交总台数
+3、报废车不纳入统计
+4、限定门店自拍账号不纳入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(门店账号待丽君2次确认，以下是车源部门提供的登录账号）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4" tint="0.4"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nndz2、nnlh2、nnft2、nndb2
+nnym2、nncm2、nnbk2、nnxd2
+nnad2、nnzj2、lzdz、lzcm2
+gldz2、glsz2
+gllh、gldb2、glcm2、glad2
+fcrc2、bhdz2、bsdz2、bsdb2
+zssd2、sjdz2、sdad2、sdwew
+dgad2、dgwew、zhlh2
+glesc、nnesc</t>
+    </r>
+  </si>
+  <si>
+    <t>长久集团</t>
+  </si>
+  <si>
+    <t>按年度，超额累进制：
+成交台数≤2500, 200元/台
+2500＜成交台数≤3500, 300元/台
+3500＜成交台数, 400元/台
+不适用于报废车
+不适用于长久集团二手车中心所拍中的车辆</t>
+  </si>
+  <si>
+    <t>2026年7月31日
+协议期满双方可就合作事宜重新商议，如未签订新协议且未就本协议提出异议，视为双方同意本协议自动延期。
+成交台数是按照合同年度，非自然年度计算</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">订单清分后统计成交车辆：
+1、集团=昊诚集团
+2、成交台数(不抛仲裁退车)：按照合同年计算；比如26年的成交台数中的合同年指统计：2025.7.31-至今的成交总台数
+3、报废车和非报废车标准不同
+4、限定门店自拍账号不纳入(系统不展示自拍账号)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(昊城自拍买家账号
+郝彩峰18210988593
+申文雪13631444109）</t>
+    </r>
+  </si>
+  <si>
+    <t>昊诚集团</t>
+  </si>
+  <si>
+    <t>非报废车：
+按年度，超额累进制：
+成交台数≤1000, 150元/台
+1000＜成交台数≤2000, 200元/台
+2000＜成交台数, 300元/台
+报废车：
+150元/台
+不适用于昊城二手车拍中的昊城门店置换车</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2028年8月31日
+协议期满双方可就合作事宜重新商议，如未签订新协议且未就本协议提出异议，视为双方同意本协议自动延期。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>成交台数是按照合同年度，非自然年度计算</t>
+    </r>
+  </si>
+  <si>
+    <t>次月1日0点统计成交车辆：
+1、门店id=4447，门店全称：桂林长久鑫广达二手车销售有限公司
+2、门店每月总费用2500元/月；
+3、每台车平均业务合作费(2500/成交台次)汇总=2500元/月</t>
+  </si>
+  <si>
+    <t>桂林长久鑫广达二手车销售有限公司</t>
+  </si>
+  <si>
+    <t>固定：2500元/月</t>
+  </si>
+  <si>
+    <t>次月1日0点统计成交车辆：
+1、门店id=4448，门店全称：广西长久二手车销售有限公司
+2、门店每月总费用4500元/月；
+3、每台车平均业务合作费(2500/成交台次)汇总=2500元/月</t>
+  </si>
+  <si>
+    <t>广西长久二手车销售有限公司</t>
+  </si>
+  <si>
+    <t>固定：4500元/月</t>
+  </si>
+  <si>
+    <t>订单清分后统计成交车辆：
+1、门店总店=吉利
+2、车辆已关联厂家</t>
+  </si>
+  <si>
+    <t>吉利</t>
+  </si>
+  <si>
+    <t>100元/台</t>
+  </si>
+  <si>
+    <t>订单清分后统计成交车辆：
+1、门店总店=广汽本田、捷途、爱咖
+2、车辆已关联厂家</t>
+  </si>
+  <si>
+    <t>广汽本田、奇瑞汽车(未接入)、捷途汽车、爱咖汽车品牌</t>
+  </si>
+  <si>
+    <t>订单清分后统计成交车辆：
+1、门店总店=一汽奔腾
+2、车辆已关联厂家</t>
+  </si>
+  <si>
+    <t>奔腾</t>
+  </si>
+  <si>
+    <t>150元/台</t>
   </si>
 </sst>
 </file>
@@ -429,7 +661,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,14 +678,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF417FF9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF417FF9"/>
+      <color theme="4"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -602,8 +834,22 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="0.4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -612,6 +858,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -797,7 +1049,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -807,8 +1059,45 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -830,8 +1119,17 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -839,14 +1137,36 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -974,7 +1294,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -986,145 +1306,211 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1651,84 +2037,299 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="25.9519230769231" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="25.9519230769231" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="3" width="25.9519230769231" customWidth="1"/>
-    <col min="4" max="4" width="34.6153846153846" customWidth="1"/>
-    <col min="5" max="16384" width="25.9519230769231" customWidth="1"/>
+    <col min="1" max="1" width="32.6923076923077" customWidth="1"/>
+    <col min="2" max="2" width="51.0096153846154" customWidth="1"/>
+    <col min="3" max="3" width="36.9903846153846" customWidth="1"/>
+    <col min="4" max="4" width="38.7788461538462" customWidth="1"/>
+    <col min="5" max="5" width="29.3269230769231" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="16384" width="25.9519230769231" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="135" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:5">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="5" t="s">
+    <row r="2" ht="84" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>4</v>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:5">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>4</v>
+    <row r="3" ht="34" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" ht="51" spans="1:5">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="6" t="s">
+    <row r="4" ht="135" spans="1:6">
+      <c r="A4" s="2"/>
+      <c r="B4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="5" ht="79" customHeight="1" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="3"/>
+    <row r="5" ht="51" spans="1:6">
+      <c r="A5" s="2"/>
+      <c r="B5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="34" spans="1:6">
+      <c r="A6" s="2"/>
+      <c r="B6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="51" spans="1:6">
+      <c r="A7" s="2"/>
+      <c r="B7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="144" customHeight="1" spans="1:6">
+      <c r="A8" s="2"/>
+      <c r="B8" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="29"/>
+      <c r="F8" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="84" spans="1:6">
+      <c r="A9" s="2"/>
+      <c r="B9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" ht="309" customHeight="1" spans="1:6">
+      <c r="A10" s="2"/>
+      <c r="B10" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="188" customHeight="1" spans="1:6">
+      <c r="A11" s="2"/>
+      <c r="B11" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="101" spans="1:6">
+      <c r="A12" s="2"/>
+      <c r="B12" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="101" spans="1:6">
+      <c r="A13" s="2"/>
+      <c r="B13" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" ht="51" spans="1:6">
+      <c r="A14" s="2"/>
+      <c r="B14" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="30"/>
+      <c r="F14" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1" spans="1:6">
+      <c r="A15" s="2"/>
+      <c r="B15" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="30"/>
+      <c r="F15" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" ht="51" spans="1:6">
+      <c r="A16" s="2"/>
+      <c r="B16" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="30"/>
+      <c r="F16" s="28" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="B1:B5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/业务合作费.xlsx
+++ b/业务合作费.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11460"/>
+    <workbookView windowWidth="31820" windowHeight="21400"/>
   </bookViews>
   <sheets>
     <sheet name="业务合作费" sheetId="1" r:id="rId1"/>
@@ -506,7 +506,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">(门店账号待丽君2次确认，以下是车源部门提供的登录账号）
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -546,11 +546,18 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">订单清分后统计成交车辆：
 1、集团=昊诚集团
 2、成交台数(不抛仲裁退车)：按照合同年计算；比如26年的成交台数中的合同年指统计：2025.7.31-至今的成交总台数
 3、报废车和非报废车标准不同
-4、限定门店自拍账号不纳入(系统不展示自拍账号)
+4、限定门店自拍账号不纳入
 </t>
     </r>
     <r>
@@ -581,6 +588,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">2028年8月31日
 协议期满双方可就合作事宜重新商议，如未签订新协议且未就本协议提出异议，视为双方同意本协议自动延期。
 </t>
@@ -1418,7 +1432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1467,9 +1481,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1490,9 +1501,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2080,10 +2088,10 @@
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2098,10 +2106,10 @@
       <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2116,10 +2124,10 @@
       <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2134,10 +2142,10 @@
       <c r="D5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2152,10 +2160,10 @@
       <c r="D6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2170,46 +2178,46 @@
       <c r="D7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" ht="144" customHeight="1" spans="1:6">
       <c r="A8" s="2"/>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="28" t="s">
+      <c r="E8" s="27"/>
+      <c r="F8" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" ht="84" spans="1:6">
       <c r="A9" s="2"/>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28" t="s">
+      <c r="E9" s="25"/>
+      <c r="F9" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="309" customHeight="1" spans="1:6">
       <c r="A10" s="2"/>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -2218,16 +2226,16 @@
       <c r="D10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" ht="188" customHeight="1" spans="1:6">
       <c r="A11" s="2"/>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -2236,16 +2244,16 @@
       <c r="D11" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" ht="101" spans="1:6">
       <c r="A12" s="2"/>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -2254,16 +2262,16 @@
       <c r="D12" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" ht="101" spans="1:6">
       <c r="A13" s="2"/>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="14" t="s">
@@ -2272,16 +2280,16 @@
       <c r="D13" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" ht="51" spans="1:6">
       <c r="A14" s="2"/>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>47</v>
       </c>
       <c r="C14" s="14" t="s">
@@ -2290,40 +2298,40 @@
       <c r="D14" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="28" t="s">
+      <c r="E14" s="28"/>
+      <c r="F14" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" ht="55" customHeight="1" spans="1:6">
       <c r="A15" s="2"/>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>51</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="28" t="s">
+      <c r="E15" s="28"/>
+      <c r="F15" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" ht="51" spans="1:6">
       <c r="A16" s="2"/>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="28"/>
+      <c r="F16" s="26" t="s">
         <v>26</v>
       </c>
     </row>
